--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/UTAH_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/UTAH_2014.xlsx
@@ -1867,7 +1867,7 @@
         <v>9</v>
       </c>
       <c r="D84">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="85">
@@ -1885,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="D85">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="86">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C103">
@@ -2389,7 +2389,7 @@
         <v>9</v>
       </c>
       <c r="D113">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="114">
@@ -2893,7 +2893,7 @@
         <v>9</v>
       </c>
       <c r="D141">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="142">
@@ -4495,7 +4495,7 @@
         <v>9</v>
       </c>
       <c r="D230">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="231">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C245">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C253">
@@ -5935,7 +5935,7 @@
         <v>9</v>
       </c>
       <c r="D310">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="311">
@@ -6007,7 +6007,7 @@
         <v>9</v>
       </c>
       <c r="D314">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="315">
@@ -6061,7 +6061,7 @@
         <v>9</v>
       </c>
       <c r="D317">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="318">
@@ -6781,7 +6781,7 @@
         <v>9</v>
       </c>
       <c r="D357">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="358">
@@ -6997,7 +6997,7 @@
         <v>9</v>
       </c>
       <c r="D369">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="370">
@@ -7339,7 +7339,7 @@
         <v>9</v>
       </c>
       <c r="D388">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="389">
@@ -8581,7 +8581,7 @@
         <v>9</v>
       </c>
       <c r="D457">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="458">
@@ -9049,7 +9049,7 @@
         <v>9</v>
       </c>
       <c r="D483">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="484">
@@ -9949,7 +9949,7 @@
         <v>9</v>
       </c>
       <c r="D533">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="534">
@@ -10057,7 +10057,7 @@
         <v>9</v>
       </c>
       <c r="D539">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="540">
@@ -10957,7 +10957,7 @@
         <v>9</v>
       </c>
       <c r="D589">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="590">
@@ -10975,7 +10975,7 @@
         <v>9</v>
       </c>
       <c r="D590">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="591">
@@ -11353,7 +11353,7 @@
         <v>9</v>
       </c>
       <c r="D611">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="612">
@@ -11515,7 +11515,7 @@
         <v>9</v>
       </c>
       <c r="D620">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="621">
@@ -11749,7 +11749,7 @@
         <v>9</v>
       </c>
       <c r="D633">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="634">
@@ -11875,7 +11875,7 @@
         <v>9</v>
       </c>
       <c r="D640">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="641">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C700">
@@ -13927,7 +13927,7 @@
         <v>9</v>
       </c>
       <c r="D754">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="755">
@@ -14665,7 +14665,7 @@
         <v>9</v>
       </c>
       <c r="D795">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="796">
@@ -17329,7 +17329,7 @@
         <v>9</v>
       </c>
       <c r="D943">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="944">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1008">
@@ -18625,7 +18625,7 @@
         <v>9</v>
       </c>
       <c r="D1015">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="1016">
@@ -19147,7 +19147,7 @@
         <v>9</v>
       </c>
       <c r="D1044">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="1045">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1106">
@@ -21307,7 +21307,7 @@
         <v>9</v>
       </c>
       <c r="D1164">
-        <v>0.000904613528998</v>
+        <v>0.0009046135289980002</v>
       </c>
     </row>
     <row r="1165">
